--- a/data/availability/projects/palm-hills-developments/hacienda-west.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-west.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Hacienda West</t>
+          <t>Live inventory for hacienda-west</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,256 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>111</v>
+      </c>
+      <c r="F2" t="n">
+        <v>111</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>112</v>
+      </c>
+      <c r="F3" t="n">
+        <v>179</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="H3" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>127</v>
+      </c>
+      <c r="F4" t="n">
+        <v>127</v>
+      </c>
+      <c r="G4" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>339</v>
+      </c>
+      <c r="F6" t="n">
+        <v>339</v>
+      </c>
+      <c r="G6" t="n">
+        <v>118.86</v>
+      </c>
+      <c r="H6" t="n">
+        <v>118.86</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +877,934 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WST-BLA-4741</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>111</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>24817250</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WST-BLA-4742</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>111</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>24678800</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WST-BLA-4743</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>111</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>24678800</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WST-BLA-4744</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>111</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>24678800</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WST-BLA-4745</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>111</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>24678800</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WST-LDG-512-M</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>112</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>37872880</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WST-LDG-514-M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>112</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>37872880</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WST-LDG-516</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>39384800</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WST-LDG-517-M</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>118</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>38730820</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WST-LDG-518</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>118</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>38730820</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WST-LDG-519</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>179</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>56416580</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WST-CAB-B057</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>127</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Garden: 102 sqm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>84256790</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cabin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WST-CAB-B058</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>127</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Garden: 102 sqm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>84256790</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WST-SCH-176AG</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>205</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Garden: 272.4 sqm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>37011151</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WST-SCH-178BG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>205</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Garden: 272.4 sqm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>36259581</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hacienda-west</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WST-VL5-07</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hacienda West (1)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>339</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>118865000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/palm-hills-developments/hacienda-west.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-west.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for hacienda-west</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +919,6 @@
       <c r="G2" t="n">
         <v>111.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -966,7 +975,6 @@
       <c r="G3" t="n">
         <v>111</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1023,7 +1031,6 @@
       <c r="G4" t="n">
         <v>111</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1080,7 +1087,6 @@
       <c r="G5" t="n">
         <v>111</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1137,7 +1143,6 @@
       <c r="G6" t="n">
         <v>111</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1194,7 +1199,6 @@
       <c r="G7" t="n">
         <v>112</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1205,7 +1209,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1227,7 +1231,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1251,7 +1255,6 @@
       <c r="G8" t="n">
         <v>120</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1262,7 +1265,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1284,7 +1287,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1308,7 +1311,6 @@
       <c r="G9" t="n">
         <v>118</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1319,7 +1321,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1341,7 +1343,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1365,7 +1367,6 @@
       <c r="G10" t="n">
         <v>118</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1376,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1398,7 +1399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1422,7 +1423,6 @@
       <c r="G11" t="n">
         <v>179</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1479,7 +1479,6 @@
       <c r="G12" t="n">
         <v>127</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1490,7 +1489,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1512,7 +1511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1536,7 +1535,6 @@
       <c r="G13" t="n">
         <v>127</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1547,7 +1545,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1593,7 +1591,6 @@
       <c r="G14" t="n">
         <v>205.02</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1604,7 +1601,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1626,7 +1623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1650,7 +1647,6 @@
       <c r="G15" t="n">
         <v>339.9</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1661,7 +1657,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
